--- a/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Más clientela el segundo verano, las tartas heladas por encargo y el canal de restaurantes ya rodados. El libro lo aplica a los clientes y también al coste de personal</t>
+          <t>Más clientela el segundo verano, las tartas heladas por encargo y el canal de restaurantes ya rodados. Se aplica a los clientes; el personal NO sube con este porcentaje: crece con las incorporaciones que declares en la hoja Personal (6.000 € el año 2 y otros 6.000 € el año 3)</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dos meses de renta antes de abrir: la obra del obrador, el aumento de potencia a trifásica y la declaración responsable</t>
+          <t>Dos meses de renta antes de abrir: la obra del obrador, el aumento de potencia a trifásica y la declaración responsable. Si el banco te da el préstamo al empezar la obra, súmale los intereses de esos meses (en el caso, unos 1.290 €), que este libro no cuenta, y ten en cuenta que la carencia corre desde la firma</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D13" s="28" t="inlineStr">
         <is>
-          <t>Las marcas profesionales no publican tarifa: estimación del kit. Una vertical de entrada de 26-30 l/h cuesta unos 4.200 € sin IVA, si empiezas con poco</t>
+          <t>Estimación del kit en la parte baja de lo publicado (12.000-35.000 €), porque las marcas profesionales no publican tarifa: pide al menos dos presupuestos antes de cerrar el préstamo. Una vertical de entrada de 26-30 l/h cuesta unos 4.200 € sin IVA, si empiezas con poco</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
-          <t>Dos módulos ventilados de -20/-9 °C con gas R290 (unos 5.090 € cada uno en la tarifa del fabricante). Con 18 cubetas en verano y 10-12 en invierno basta en una ciudad media</t>
+          <t>Dos módulos ventilados de 10 cubetas, de -20/-9 °C y con gas R290 (unos 5.090 € cada uno en la tarifa del fabricante): 18 sabores y dos huecos para el sabor del día o la reserva. Con 18 sabores en verano y 10-12 en invierno basta en una ciudad media</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="J5" s="28" t="inlineStr">
         <is>
-          <t>Balancea las mezclas, pasteuriza, manteca y abate, compra y lleva la gestión. Como administrador de la SL cotiza en el régimen de autónomos: confirma con tu gestoría la cuota y si te aplica la reducida de inicio</t>
+          <t>Balancea las mezclas, pasteuriza, manteca y abate, compra y lleva la gestión. Como administrador de la SL cotiza en el régimen de autónomos: el libro le imputa el 33 % de Seguridad Social sobre 14 pagas como si fuera nómina (con este bruto, unos 8.085 € al año), que es el lado prudente. Confirma con tu gestoría la cuota real y si te aplica la reducida de inicio</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="O13" s="28" t="inlineStr">
         <is>
-          <t>Doce mensualidades más las pagas extra en los meses que digas en Supuestos. La suma del año es la misma que la del P&amp;L. El personal se reparte en doce meses, pero los fijos discontinuos de temporada sólo cobran de abril a septiembre: el invierno sale aquí más caro que en la realidad, que es el lado prudente</t>
+          <t>Doce mensualidades más las pagas extra en los meses que digas en Supuestos. La suma del año es la misma que la del P&amp;L. El personal se reparte en doce meses, pero los fijos discontinuos de temporada sólo cobran de abril a septiembre: aquí el invierno sale más caro y el verano más barato que en la realidad. El saldo de marzo y el de febrero apenas cambian, pero de junio a enero tu caja real será menor que la de esta hoja (en el caso, hasta unos 10.000 € menos en septiembre)</t>
         </is>
       </c>
     </row>
@@ -8742,10 +8742,10 @@
       <c r="N33" s="28" t="n"/>
       <c r="O33" s="28" t="n"/>
     </row>
-    <row r="34" ht="120" customHeight="1">
+    <row r="34" ht="225" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>El IVA del cuarto trimestre se liquida en enero del año siguiente, así que no aparece en este cuadro. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
+          <t>Los trimestres de esta hoja son de tres meses del plan (marzo-mayo, junio-agosto y septiembre-noviembre), no los naturales: con el Mes 1 en marzo, el modelo 303 se presenta en abril (por marzo), julio, octubre y enero (por octubre-diciembre, ya en el Mes 11). En el caso todos los trimestres salen a compensar y no mueven la caja; a 31 de diciembre quedan unos 17.750 € por compensar, que puedes pedir como devolución en el 303 de enero. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
         <v>0.020533968475303872</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y "&amp;"ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, "&amp;"Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 51624 € de los 158274 € de inversión.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -2753,7 +2753,7 @@
         <v>0.18000000000000002</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las "&amp;"pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas","")</f>
         <v>Al 20% de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas</v>
       </c>
       <c r="G13" s="75" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/plan-financiero-heladeria.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
         <v>0.020533968475303872</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y "&amp;"ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Obra y acondicionamiento del obrador y la tienda, Instalación eléctrica trifásica, cuadro y boletín, Fontanería, desagües, climatización y ventilación y Rótulo y escaparate), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, "&amp;"Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Formación técnica de heladería, Marca, web, fotos y lanzamiento, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Stock inicial de materias primas y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 51624 € de los 158274 € de inversión.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -2753,7 +2753,7 @@
         <v>0.18000000000000002</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las "&amp;"pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas","")</f>
         <v>Al 20% de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar: la leche, los huevos, la fruta y los quesos van al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y la nata, el azúcar, el chocolate, las pastas y los barquillos al 10 %; con un 30 % de la compra al 4 % sale un 8,2 %. Ajústalo a tus facturas</v>
       </c>
       <c r="G13" s="75" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
